--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T19:01:50+00:00</t>
+    <t>2026-10-30T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T07:50:37+00:00</t>
+    <t>2026-10-30T09:25:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T09:25:40+00:00</t>
+    <t>2026-10-30T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-referenz.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T10:55:39+00:00</t>
+    <t>2026-10-30T14:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
